--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -762,7 +762,311 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 11:44 AM IST</t>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13225650 / 2320250 (5.7x)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>515.3</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>488.4</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>583.1</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>614.7</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>477.5499877929688</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.510.5 above EMA200 Rs.496.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 515.3</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>368.1499938964844</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9390241 / 5382027 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>419.3</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>361.6000061035156</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.368.1 above EMA200 Rs.355.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 368.9</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1153.900024414062</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1164484 / 860243 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1171.5</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1089.1</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>1336.2</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1418.6</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>1112.5</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>1171.5</v>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1153.9 above EMA200 Rs.977.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 50 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1159.9</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>295.8500061035156</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48001304 / 38531770 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>278.9</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.295.9 above EMA200 Rs.267.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 297.0</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026 06:52 PM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,538 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>HEXT</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>593.1500244140625</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9864399 / 1157952 (8.5x)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>619.8</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>626</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>576.5</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>725</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>774.6</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>562.9500122070312</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>626</v>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.593.2 above EMA200 Rs.569.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 8.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 8.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 619.8</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>238.1399993896484</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20864618 / 2455217 (8.5x)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>245.4</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>231.3</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>221.4499969482422</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.238.1 above EMA200 Rs.195.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 8.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 8.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 245.4</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1491.800048828125</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5464860 / 2115781 (2.6x)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1507.2</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1448.7</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>1655.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>1723.9</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>1446.099975585938</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1491.8 above EMA200 Rs.1329.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1507.2</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1040.900024414062</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7160194 / 5485153 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1051</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1060.4</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>997.9</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>1185.4</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>1247.9</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>1038.199951171875</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>1060.4</v>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1040.9 above EMA200 Rs.924.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1051.0</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1163.900024414062</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1088896 / 824910 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1174.8</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1183.6</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1125.3</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1300.3</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>1358.6</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1162.400024414062</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>1183.6</v>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1163.9 above EMA200 Rs.1131.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1174.8</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>582.3499755859375</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2903322 / 2171581 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>594.4</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>600.3</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>683.9</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>725.7</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>573.2000122070312</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>600.3</v>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.582.3 above EMA200 Rs.500.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 594.4</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>883.25</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2384426 / 1909810 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>886.3</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>891.4</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>857.6</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>959</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>992.8</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>858.6500244140625</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>891.4</v>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.883.2 above EMA200 Rs.784.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 886.3</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1602,6 +1602,82 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2026 05:52 PM IST</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1802.900024414062</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2713424 / 1433855 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1839.6</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1856.2</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1745.5</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>2077.7</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>2188.4</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>1753</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>1856.2</v>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1802.9 above EMA200 Rs.1636.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1839.6</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2026 05:52 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1678,6 +1678,234 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3283.699951171875</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4851804 / 2312126 (2.1x)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>3327</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>3350</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3196.5</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>3657.1</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>3810.6</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>3221.800048828125</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>3350</v>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3283.7 above EMA200 Rs.3210.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3327.0</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>906.8499755859375</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1646157 / 840344 (2.0x)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>921.8</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>929.4</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>878.7</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1030.9</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>1081.6</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>882.9000244140625</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>929.4</v>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.906.8 above EMA200 Rs.869.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.0x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.0x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 921.8</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8651992 / 5972648 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0.08199999999999999</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.333.8 above EMA200 Rs.269.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 334.2</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:34 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1906,538 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>404.2999877929688</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10947397 / 3377063 (3.2x)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>413</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>416.1</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>457.3</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>477.9</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>394.0499877929688</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>416.1</v>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.404.3 above EMA200 Rs.344.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 56 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 413.0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>489.1000061035156</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11291944 / 772606 (14.6x)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>517</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>521.9</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>488.6</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.064</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>588.5</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>621.9</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>480.2000122070312</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>521.9</v>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.489.1 above EMA200 Rs.444.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 14.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 14.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 517.0</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3398.5</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6129983 / 2423507 (2.5x)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>3457</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>3482.7</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>3311.1</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>3826</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>3997.6</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>3283.699951171875</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>3482.7</v>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3398.5 above EMA200 Rs.3212.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3457.0</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>BELRISE</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>236.7299957275391</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9505308 / 4980886 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>243.1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>245.1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>286</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>232.7899932861328</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>245.1</v>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.236.7 above EMA200 Rs.196.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 243.1</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1849.900024414062</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2944366 / 1535886 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1863.1</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1881.1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1761.3</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.064</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>2120.7</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>2240.5</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>1773.800048828125</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>1881.1</v>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1849.9 above EMA200 Rs.1640.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1863.1</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>5122.7998046875</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1427803 / 850238 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5140.7</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5189.1</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>4866.2</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>5834.8</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>6157.7</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>4872.10009765625</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>5189.1</v>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.5122.8 above EMA200 Rs.4241.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 5140.7</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2199.800048828125</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>952011 / 740595 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2212.6</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2226.8</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>2132.2</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>2416</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>2510.6</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>2164.699951171875</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>2226.8</v>
+      </c>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2199.8 above EMA200 Rs.1767.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2212.6</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>31/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2438,6 +2438,310 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>646.7999877929688</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3161226 / 690588 (4.6x)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>665.5</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>672.1</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>627.8</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>805</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>586.2000122070312</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>672.1</v>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.646.8 above EMA200 Rs.523.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 4.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 4.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 665.5</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>371.1000061035156</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>3055816 / 1969722 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>362.6000061035156</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.371.1 above EMA200 Rs.297.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 376.4</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1292.300048828125</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2577547 / 1683367 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1304.5</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1262.1</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>1411.8</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>1461.7</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>1270</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1292.3 above EMA200 Rs.1199.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1304.5</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8868042 / 6818867 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>326.5</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>326.5</v>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.318.0 above EMA200 Rs.277.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 324.1</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 06:51 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2742,6 +2742,158 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1585.900024414062</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2242896 / 841071 (2.7x)</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1591.8</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1603</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1529.1</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>1750.8</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>1824.7</v>
+      </c>
+      <c r="N30" s="8" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>1554.699951171875</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>1603</v>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1585.9 above EMA200 Rs.1365.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1591.8</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>710.0499877929688</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>7525410 / 1386596 (5.4x)</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>718</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>725.2</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>670.7</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>834.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>888.6</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>657.9500122070312</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>725.2</v>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.710.0 above EMA200 Rs.629.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 718.0</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2894,6 +2894,386 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>227.3500061035156</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2932541 / 1246338 (2.4x)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>262.3</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>216.1399993896484</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.227.4 above EMA200 Rs.220.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 229.0</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>14286588 / 6048418 (2.4x)</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2040.8</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1975.3</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>2171.8</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>2237.3</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>1970.099975585938</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>2040.8</v>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1978.0 above EMA200 Rs.1888.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2031.0</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>USHAMART</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>520.25</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>924202 / 528497 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>522.6</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>526.9</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>584.7</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>613.7</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>503.6000061035156</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>526.9</v>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.520.2 above EMA200 Rs.450.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 522.6</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1982973 / 1140169 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1665</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1675.9</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1603.5</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>1820.6</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>1675.9</v>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1665.0 above EMA200 Rs.1487.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1665.0</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3224</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>692487 / 516863 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>3260</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>3279.7</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>3148.3</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>3542.5</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>3673.9</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>3138</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>3279.7</v>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3224.0 above EMA200 Rs.2933.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3260.0</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 05:47 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3274,6 +3274,82 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>504.9500122070312</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1783049 / 1304285 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>506.7</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>481.3</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>570.9</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>600.8</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>485.9500122070312</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.505.0 above EMA200 Rs.447.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 506.7</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 05:50 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3350,6 +3350,234 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>131.5899963378906</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>12677374 / 5960083 (2.1x)</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="N38" s="8" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>125.4899978637695</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.131.6 above EMA200 Rs.123.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 133.5</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2265.199951171875</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1151904 / 764818 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>2270</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>2283.2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2194.9</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>2459.7</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>2548</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>2210</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>2283.2</v>
+      </c>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2265.2 above EMA200 Rs.1790.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2270.0</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>183.6000061035156</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>22184599 / 17893728 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.183.6 above EMA200 Rs.161.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 184.9</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3578,6 +3578,234 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>RHIM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>423.3500061035156</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1616351 / 554472 (2.9x)</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>437</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>410.2</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>490.6</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>517.4</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>412.7999877929688</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.423.4 above EMA200 Rs.413.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 433.0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1282</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5800161 / 1695066 (3.4x)</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1298.5</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1309.9</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>1234</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>1461.7</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>1225.300048828125</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>1309.9</v>
+      </c>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1282.0 above EMA200 Rs.1147.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1298.5</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>453</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>8391217 / 3263978 (2.6x)</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>466.1</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>441.9</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>514.4</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>538.6</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>442.7999877929688</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>466.1</v>
+      </c>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.453.0 above EMA200 Rs.446.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 56 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 462.5</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 04:57 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3806,6 +3806,234 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>970.25</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>8416350 / 895023 (9.4x)</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>974</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>983.2</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>922</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>1166.8</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>897.7000122070312</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>983.2</v>
+      </c>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.970.2 above EMA200 Rs.875.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 9.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 9.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 974.0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>MRPL</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>181.1399993896484</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>57502291 / 22033062 (2.6x)</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>162.9600067138672</v>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="R45" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.181.1 above EMA200 Rs.160.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 183.0</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1733</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>3109398 / 1233632 (2.5x)</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1747</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1761.7</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>1663.5</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>1958.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>2056.3</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>1630</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>1761.7</v>
+      </c>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1733.0 above EMA200 Rs.1640.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1747.0</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 04:35 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4034,6 +4034,158 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1701.5</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1724546 / 1323393 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>1701.5</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1712</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>1641.9</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>1852.2</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0.08199999999999999</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>1922.3</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>1685.800048828125</v>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>1712</v>
+      </c>
+      <c r="R47" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1701.5 above EMA200 Rs.1496.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1701.5</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>22002118 / 17159238 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>217</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.187.0 above EMA200 Rs.162.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 70 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 187.6</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4186,6 +4186,82 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>13/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>533.6500244140625</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>4783085 / 2221179 (2.2x)</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>539.8</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>511</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>597.3</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>512.0499877929688</v>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>539.8</v>
+      </c>
+      <c r="R49" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.533.7 above EMA200 Rs.498.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 535.5</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>13/08/2026 04:41 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4262,6 +4262,234 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1992.099975585938</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>12282326 / 6320929 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>2017.7</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>1938.6</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>2176</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="M50" s="7" t="n">
+        <v>2255.1</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>1939.099975585938</v>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>2017.7</v>
+      </c>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1992.1 above EMA200 Rs.1890.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2005.8</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>319.4500122070312</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>8035439 / 5877604 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>345</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0.07400000000000001</v>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.319.5 above EMA200 Rs.317.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 319.5</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3035.10009765625</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1666340 / 1069548 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>3048</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>3067.6</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>2937.2</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>3328.4</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>3458.8</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>2964.89990234375</v>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>3067.6</v>
+      </c>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3035.1 above EMA200 Rs.2621.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 50 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3048.0</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026 04:38 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4490,6 +4490,234 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>655.75</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1396170 / 821414 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>658.7</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>665.3</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>612.1</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>771.7</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>825</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>619.6500244140625</v>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>665.3</v>
+      </c>
+      <c r="R53" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.655.8 above EMA200 Rs.532.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 658.7</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>973</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2102591 / 1234230 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>981</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>988.3</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>939.7</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>1085.4</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>1134</v>
+      </c>
+      <c r="N54" s="8" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>940</v>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>988.3</v>
+      </c>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.973.0 above EMA200 Rs.942.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 981.0</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>435.9500122070312</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>15348223 / 10291970 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>436</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>503</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>421.7000122070312</v>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="R55" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.436.0 above EMA200 Rs.339.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 436.0</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4718,6 +4718,386 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>MINDACORP</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>745.25</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1637214 / 659153 (2.5x)</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>769</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>776.7</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>-0.07400000000000001</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>892.2</v>
+      </c>
+      <c r="L56" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>949.9</v>
+      </c>
+      <c r="N56" s="8" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>725.1500244140625</v>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>776.7</v>
+      </c>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.745.2 above EMA200 Rs.604.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 769.0</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3278.699951171875</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1498743 / 775853 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>3297.7</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>3185</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>3605</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>3745</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>3250.5</v>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>3325</v>
+      </c>
+      <c r="R57" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3278.7 above EMA200 Rs.2949.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3297.7</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>326.5499877929688</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>4673328 / 3380980 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>-0.07400000000000001</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="L58" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="N58" s="8" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>315.4500122070312</v>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="R58" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.326.5 above EMA200 Rs.309.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 329.9</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>BLUEJET</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>607.25</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1660583 / 1132241 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>613</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>619.1</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>575.7</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>706</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>593.2000122070312</v>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>619.1</v>
+      </c>
+      <c r="R59" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.607.2 above EMA200 Rs.539.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 613.0</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2587</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1229008 / 895073 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>2619.5</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>2640.6</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>2499.7</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>2922.5</v>
+      </c>
+      <c r="L60" s="8" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>3063.4</v>
+      </c>
+      <c r="N60" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>2569.699951171875</v>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>2640.6</v>
+      </c>
+      <c r="R60" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2587.0 above EMA200 Rs.2543.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2619.5</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5098,6 +5098,310 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>THELEELA</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>532.7999877929688</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1462087 / 571436 (2.6x)</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>541.8</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>507.1</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>627.4</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>667.6</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>519.1500244140625</v>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.532.8 above EMA200 Rs.449.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 541.8</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>631.5499877929688</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>4251654 / 2400008 (1.8x)</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>640.5</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>645.9</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>609.9</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="L62" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M62" s="7" t="n">
+        <v>753.8</v>
+      </c>
+      <c r="N62" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>627.0499877929688</v>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>645.9</v>
+      </c>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.631.5 above EMA200 Rs.550.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 640.5</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>380.3999938964844</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2120946 / 1744208 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>387</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>435.3</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M63" s="7" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="R63" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.380.4 above EMA200 Rs.307.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 387.0</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1140801 / 899382 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>1121.8</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>1129</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>1080.7</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>1225.5</v>
+      </c>
+      <c r="L64" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>1273.8</v>
+      </c>
+      <c r="N64" s="8" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>1101.5</v>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>1129</v>
+      </c>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1115.0 above EMA200 Rs.1109.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 56 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1121.8</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026 04:17 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T64"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5402,6 +5402,386 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>397.3999938964844</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>9461189 / 1816321 (5.2x)</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>406.5</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>410.3</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="M65" s="7" t="n">
+        <v>485.4</v>
+      </c>
+      <c r="N65" s="8" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>380.3999938964844</v>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>410.3</v>
+      </c>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.397.4 above EMA200 Rs.307.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 406.5</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1299.699951171875</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>3416190 / 1463007 (2.3x)</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>1310.6</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1318.4</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>1266.5</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>1422.2</v>
+      </c>
+      <c r="L66" s="8" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>1474.1</v>
+      </c>
+      <c r="N66" s="8" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>1285.800048828125</v>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>1318.4</v>
+      </c>
+      <c r="R66" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1299.7 above EMA200 Rs.1212.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1310.6</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1748384 / 949321 (1.8x)</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>1232</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>1171.1</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>1353.9</v>
+      </c>
+      <c r="L67" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M67" s="7" t="n">
+        <v>1414.8</v>
+      </c>
+      <c r="N67" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1203.0 above EMA200 Rs.1099.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1222.9</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>566.7000122070312</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1256693 / 724174 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>576</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>581.8</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>549.3</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="L68" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M68" s="7" t="n">
+        <v>679.3</v>
+      </c>
+      <c r="N68" s="8" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>565.5999755859375</v>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>581.8</v>
+      </c>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.566.7 above EMA200 Rs.518.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 576.0</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1182174 / 824244 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>3310</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>3338.3</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>3204.9</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>3605.1</v>
+      </c>
+      <c r="L69" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M69" s="7" t="n">
+        <v>3738.5</v>
+      </c>
+      <c r="N69" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>3270</v>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>3338.3</v>
+      </c>
+      <c r="R69" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3300.0 above EMA200 Rs.2961.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3310.0</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026 04:18 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5782,6 +5782,386 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>296.9500122070312</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>4338188 / 851274 (5.1x)</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="L70" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M70" s="7" t="n">
+        <v>382</v>
+      </c>
+      <c r="N70" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>282.6000061035156</v>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="R70" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.297.0 above EMA200 Rs.247.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 305.0</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1388.900024414062</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>3741472 / 991079 (3.8x)</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>1401.8</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>1409.9</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>1356.1</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>1517.4</v>
+      </c>
+      <c r="L71" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M71" s="7" t="n">
+        <v>1571.2</v>
+      </c>
+      <c r="N71" s="8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>1345.900024414062</v>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>1409.9</v>
+      </c>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1388.9 above EMA200 Rs.1345.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1401.8</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>291.6499938964844</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>16800852 / 1020979 (16.5x)</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M72" s="7" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="N72" s="8" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>269.75</v>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="R72" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.291.6 above EMA200 Rs.227.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 70 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 16.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 16.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 298.4</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>3308</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1465187 / 866982 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>3343.1</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>3369.8</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>3206.9</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>3695.6</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>3858.5</v>
+      </c>
+      <c r="N73" s="8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>3369.8</v>
+      </c>
+      <c r="R73" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3308.0 above EMA200 Rs.2963.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3343.1</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>CANHLIFE</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>155.2400054931641</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>794508 / 606559 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="N74" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>151.6900024414062</v>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.155.2 above EMA200 Rs.138.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 155.8</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026 04:19 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6162,6 +6162,234 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>445.8500061035156</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>5256920 / 822500 (6.4x)</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>467.4</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>470.7</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>514</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M75" s="7" t="n">
+        <v>535.7</v>
+      </c>
+      <c r="N75" s="8" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O75" s="4" t="n">
+        <v>439.7000122070312</v>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>470.7</v>
+      </c>
+      <c r="R75" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.445.9 above EMA200 Rs.440.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 6.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 6.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 467.4</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>ENGINERSIN</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>254.8300018310547</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>5605769 / 2285759 (2.5x)</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>296.7</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="N76" s="8" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>244.9100036621094</v>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="R76" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.254.8 above EMA200 Rs.222.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 256.5</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1327</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>3648035 / 1546548 (2.4x)</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>1327</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>1334.8</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>1282.6</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>1439.2</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>1491.4</v>
+      </c>
+      <c r="N77" s="8" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>1293.699951171875</v>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>1334.8</v>
+      </c>
+      <c r="R77" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1327.0 above EMA200 Rs.1215.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1327.0</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 04:24 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6390,6 +6390,386 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>PARADEEP</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>159.6300048828125</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>51528268 / 13135748 (3.9x)</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="L78" s="8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>189.8</v>
+      </c>
+      <c r="N78" s="8" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>149.3999938964844</v>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="R78" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.159.6 above EMA200 Rs.141.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 160.6</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>203.0099945068359</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>53173920 / 24718623 (2.2x)</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>196.3</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>227.8</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="N79" s="8" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>196.4700012207031</v>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="R79" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.203.0 above EMA200 Rs.180.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 205.2</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>346</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2921717 / 1612533 (1.8x)</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="N80" s="8" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>338.1499938964844</v>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="R80" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.346.0 above EMA200 Rs.288.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 347.9</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2610</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1638486 / 938037 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>2621.7</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>2643.4</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>2915.4</v>
+      </c>
+      <c r="L81" s="8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M81" s="7" t="n">
+        <v>3051.4</v>
+      </c>
+      <c r="N81" s="8" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>2552</v>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>2643.4</v>
+      </c>
+      <c r="R81" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2610.0 above EMA200 Rs.2546.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2621.7</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1866.199951171875</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>3550471 / 2164652 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>1869.4</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>1880.7</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>1805.7</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>2030.8</v>
+      </c>
+      <c r="L82" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>2105.8</v>
+      </c>
+      <c r="N82" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>1802</v>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>1880.7</v>
+      </c>
+      <c r="R82" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1866.2 above EMA200 Rs.1294.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1869.4</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>25/08/2026 04:20 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T82"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6770,6 +6770,234 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>517</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2059504 / 1477745 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>527.7</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>565.6</v>
+      </c>
+      <c r="L83" s="8" t="n">
+        <v>0.07200000000000001</v>
+      </c>
+      <c r="M83" s="7" t="n">
+        <v>584.6</v>
+      </c>
+      <c r="N83" s="8" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>516</v>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>527.7</v>
+      </c>
+      <c r="R83" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.517.0 above EMA200 Rs.501.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 524.2</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>2625</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1703493 / 990672 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>2656.8</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>2675.8</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>2549.3</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>2928.8</v>
+      </c>
+      <c r="L84" s="8" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="M84" s="7" t="n">
+        <v>3055.3</v>
+      </c>
+      <c r="N84" s="8" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>2610</v>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>2675.8</v>
+      </c>
+      <c r="R84" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2625.0 above EMA200 Rs.2547.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2656.8</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>145.9499969482422</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>10249384 / 6070851 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M85" s="7" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="N85" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>143.9900054931641</v>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="R85" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.145.9 above EMA200 Rs.139.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 147.9</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 04:22 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -6842,7 +6842,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:22 PM IST</t>
+          <t>28/08/2026 02:02 AM IST</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:22 PM IST</t>
+          <t>28/08/2026 02:02 AM IST</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:22 PM IST</t>
+          <t>28/08/2026 02:02 AM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:T89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6998,6 +6998,310 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CANHLIFE</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>156.8899993896484</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>3945084 / 585878 (6.7x)</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>177.9</v>
+      </c>
+      <c r="L86" s="8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="N86" s="8" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>153.8800048828125</v>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="R86" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.156.9 above EMA200 Rs.139.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 6.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 6.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 159.9</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>433.9500122070312</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>19967976 / 7180056 (2.8x)</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>419</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>486.8</v>
+      </c>
+      <c r="L87" s="8" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="M87" s="7" t="n">
+        <v>509.4</v>
+      </c>
+      <c r="N87" s="8" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v>415.5</v>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="R87" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.434.0 above EMA200 Rs.346.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 62 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 438.2</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2069.39990234375</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1142681 / 565086 (2.0x)</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>2095</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>2110.5</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>2007.4</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>2316.7</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>2419.8</v>
+      </c>
+      <c r="N88" s="8" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>2035.099975585938</v>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>2110.5</v>
+      </c>
+      <c r="R88" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2069.4 above EMA200 Rs.1924.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.0x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.0x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2095.0</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1443</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>11539716 / 9338752 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>1453.8</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>1459.3</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>1422.3</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>1533.2</v>
+      </c>
+      <c r="L89" s="8" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>1570.2</v>
+      </c>
+      <c r="N89" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="O89" s="4" t="n">
+        <v>1430</v>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>1459.3</v>
+      </c>
+      <c r="R89" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1443.0 above EMA200 Rs.1360.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1453.8</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>29/08/2026 02:41 AM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T89"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7302,6 +7302,614 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>191.2299957275391</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>26274358 / 2868463 (9.2x)</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="L90" s="8" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="N90" s="8" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>185.1999969482422</v>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="R90" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.191.2 above EMA200 Rs.168.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 9.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 9.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 200.0</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1717</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2416699 / 993606 (2.4x)</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>1717</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>1726.7</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>1662</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>1856</v>
+      </c>
+      <c r="L91" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M91" s="7" t="n">
+        <v>1920.7</v>
+      </c>
+      <c r="N91" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="O91" s="4" t="n">
+        <v>1637</v>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>1726.7</v>
+      </c>
+      <c r="R91" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1717.0 above EMA200 Rs.1405.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1717.0</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>ENGINERSIN</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>261.8699951171875</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>6246235 / 2843965 (2.2x)</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>248.2</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M92" s="7" t="n">
+        <v>320.1</v>
+      </c>
+      <c r="N92" s="8" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>253.7200012207031</v>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="R92" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.261.9 above EMA200 Rs.225.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 263.5</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>1016.599975585938</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1476564 / 1010504 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1016.6</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>1021.6</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>988.2</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>1088.5</v>
+      </c>
+      <c r="L93" s="8" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="M93" s="7" t="n">
+        <v>1121.9</v>
+      </c>
+      <c r="N93" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O93" s="4" t="n">
+        <v>994</v>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>1021.6</v>
+      </c>
+      <c r="R93" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1016.6 above EMA200 Rs.920.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1016.6</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>483.1499938964844</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>4789891 / 2926879 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>476.2</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>560.2</v>
+      </c>
+      <c r="L94" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M94" s="7" t="n">
+        <v>588.2</v>
+      </c>
+      <c r="N94" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O94" s="4" t="n">
+        <v>469.8500061035156</v>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="R94" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.483.1 above EMA200 Rs.450.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 62 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 500.0</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>414.4500122070312</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>12594039 / 10139510 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="L95" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M95" s="7" t="n">
+        <v>453.8</v>
+      </c>
+      <c r="N95" s="8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O95" s="4" t="n">
+        <v>411.8999938964844</v>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="R95" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.414.5 above EMA200 Rs.413.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 414.5</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1640489 / 1259963 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>904.5</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>866.2</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>981</v>
+      </c>
+      <c r="L96" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="N96" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="O96" s="4" t="n">
+        <v>882.4000244140625</v>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>904.5</v>
+      </c>
+      <c r="R96" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.898.8 above EMA200 Rs.828.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 898.8</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>916</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>3341893 / 2381496 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>916</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>921.9</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>882.9</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L97" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M97" s="7" t="n">
+        <v>1039</v>
+      </c>
+      <c r="N97" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="O97" s="4" t="n">
+        <v>889</v>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>921.9</v>
+      </c>
+      <c r="R97" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.916.0 above EMA200 Rs.811.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 916.0</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:24 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -7374,7 +7374,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 09:24 PM IST</t>
+          <t>31/08/2026 11:08 PM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7910,6 +7910,158 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026 08:25 PM IST</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1518.099975585938</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2643709 / 556305 (4.8x)</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>1560</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>1573.2</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>1749.1</v>
+      </c>
+      <c r="L98" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M98" s="7" t="n">
+        <v>1837</v>
+      </c>
+      <c r="N98" s="8" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O98" s="4" t="n">
+        <v>1459.699951171875</v>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>1573.2</v>
+      </c>
+      <c r="R98" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1518.1 above EMA200 Rs.1126.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 4.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 4.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1560.0</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026 08:25 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026 08:25 PM IST</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>1782.800048828125</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1005805 / 592022 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>1820</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>1834.4</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>1738.7</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>2025.8</v>
+      </c>
+      <c r="L99" s="8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M99" s="7" t="n">
+        <v>2121.5</v>
+      </c>
+      <c r="N99" s="8" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="O99" s="4" t="n">
+        <v>1749.400024414062</v>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>1834.4</v>
+      </c>
+      <c r="R99" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1782.8 above EMA200 Rs.1682.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1820.0</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026 08:25 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T99"/>
+  <dimension ref="A1:T103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8062,6 +8062,310 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>199.1100006103516</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>24333313 / 4168400 (5.8x)</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>231</v>
+      </c>
+      <c r="L100" s="8" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="M100" s="7" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="N100" s="8" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>185.7700042724609</v>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="R100" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.199.1 above EMA200 Rs.169.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 201.4</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>21094953 / 13143034 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="L101" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M101" s="7" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="N101" s="8" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="O101" s="4" t="n">
+        <v>115.2200012207031</v>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="R101" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.117.0 above EMA200 Rs.110.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 117.2</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>2032.400024414062</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>966073 / 503698 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>2065.2</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>1949</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>2297.5</v>
+      </c>
+      <c r="L102" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M102" s="7" t="n">
+        <v>2413.7</v>
+      </c>
+      <c r="N102" s="8" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>1970.199951171875</v>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>2065.2</v>
+      </c>
+      <c r="R102" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2032.4 above EMA200 Rs.1831.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2047.8</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>4334029 / 3051047 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>503.8</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>478.7</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K103" s="7" t="n">
+        <v>554</v>
+      </c>
+      <c r="L103" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>579.1</v>
+      </c>
+      <c r="N103" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="O103" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>503.8</v>
+      </c>
+      <c r="R103" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.498.1 above EMA200 Rs.451.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 500.0</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:01 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T103"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8366,6 +8366,538 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>853.8499755859375</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2829025 / 545203 (5.2x)</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>873.5</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>880.6</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>833.3</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>-0.05400000000000001</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>975.3</v>
+      </c>
+      <c r="L104" s="8" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>1022.6</v>
+      </c>
+      <c r="N104" s="8" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O104" s="4" t="n">
+        <v>831.75</v>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>880.6</v>
+      </c>
+      <c r="R104" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.853.8 above EMA200 Rs.719.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 5.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 5.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 873.5</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>628.2999877929688</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>22182136 / 1576828 (14.1x)</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>640.2</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>645.7</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>609.6</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K105" s="7" t="n">
+        <v>717.9</v>
+      </c>
+      <c r="L105" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>754</v>
+      </c>
+      <c r="N105" s="8" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O105" s="4" t="n">
+        <v>588.8499755859375</v>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>645.7</v>
+      </c>
+      <c r="R105" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.628.3 above EMA200 Rs.559.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 14.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 14.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 640.2</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>JMFINANCIL</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>134.5299987792969</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>5027924 / 2733327 (1.8x)</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="L106" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M106" s="7" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="N106" s="8" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O106" s="4" t="n">
+        <v>129.3899993896484</v>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="R106" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.134.5 above EMA200 Rs.131.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 135.5</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>8137317 / 5868894 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K107" s="7" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="L107" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M107" s="7" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="N107" s="8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O107" s="4" t="n">
+        <v>143.1000061035156</v>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="R107" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.145.0 above EMA200 Rs.140.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 146.1</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2690034 / 1564987 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="K108" s="7" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="L108" s="8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M108" s="7" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="N108" s="8" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="O108" s="4" t="n">
+        <v>346.6000061035156</v>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="R108" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.350.0 above EMA200 Rs.292.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 358.0</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1694328 / 1270118 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>1244.4</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>1256.2</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>1177.4</v>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>1413.7</v>
+      </c>
+      <c r="L109" s="8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M109" s="7" t="n">
+        <v>1492.5</v>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="O109" s="4" t="n">
+        <v>1208.300048828125</v>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>1256.2</v>
+      </c>
+      <c r="R109" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1234.0 above EMA200 Rs.1082.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1244.4</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>704.3499755859375</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>8595282 / 6827149 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>722</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>729.2</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>670.9</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>845.9</v>
+      </c>
+      <c r="L110" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>904.2</v>
+      </c>
+      <c r="N110" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O110" s="4" t="n">
+        <v>669.75</v>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>729.2</v>
+      </c>
+      <c r="R110" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.704.3 above EMA200 Rs.554.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 722.0</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026 08:05 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T110"/>
+  <dimension ref="A1:T111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8898,6 +8898,82 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026 07:53 PM IST</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>190.2700042724609</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>4231051 / 2087580 (2.0x)</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>191.6</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="K111" s="7" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="L111" s="8" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="N111" s="8" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="O111" s="4" t="n">
+        <v>186.4199981689453</v>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>191.6</v>
+      </c>
+      <c r="R111" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.190.3 above EMA200 Rs.181.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 69 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.0x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.0x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 190.9</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026 07:53 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T111"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8974,6 +8974,386 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>1414.900024414062</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2731025 / 1275004 (2.1x)</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>1438</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>1448.4</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1379.2</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K112" s="7" t="n">
+        <v>1586.7</v>
+      </c>
+      <c r="L112" s="8" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="M112" s="7" t="n">
+        <v>1655.9</v>
+      </c>
+      <c r="N112" s="8" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="O112" s="4" t="n">
+        <v>1394.599975585938</v>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>1448.4</v>
+      </c>
+      <c r="R112" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1414.9 above EMA200 Rs.1365.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1438.0</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>3936393 / 2125636 (1.9x)</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>912</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>918.7</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>874.3</v>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K113" s="7" t="n">
+        <v>1007.6</v>
+      </c>
+      <c r="L113" s="8" t="n">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="M113" s="7" t="n">
+        <v>1052</v>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="O113" s="4" t="n">
+        <v>891</v>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>918.7</v>
+      </c>
+      <c r="R113" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.895.0 above EMA200 Rs.815.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 52 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 912.0</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>654.0499877929688</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>4742046 / 2784699 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>667</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>621.1</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>-0.078</v>
+      </c>
+      <c r="K114" s="7" t="n">
+        <v>778.8</v>
+      </c>
+      <c r="L114" s="8" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="M114" s="7" t="n">
+        <v>831.4</v>
+      </c>
+      <c r="N114" s="8" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="O114" s="4" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="R114" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.654.0 above EMA200 Rs.539.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 58 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 667.0</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>9909898 / 7245477 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="K115" s="7" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="L115" s="8" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="M115" s="7" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="N115" s="8" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="O115" s="4" t="n">
+        <v>173.3999938964844</v>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="R115" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.176.0 above EMA200 Rs.168.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 177.3</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>219.6600036621094</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>6405196 / 4011175 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>223.7</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>210.7</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K116" s="7" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="L116" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="M116" s="7" t="n">
+        <v>262.7</v>
+      </c>
+      <c r="N116" s="8" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O116" s="4" t="n">
+        <v>214.2200012207031</v>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>223.7</v>
+      </c>
+      <c r="R116" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.219.7 above EMA200 Rs.182.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 221.8</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 09:22 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T116"/>
+  <dimension ref="A1:T120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9354,6 +9354,310 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>328.7999877929688</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>6605790 / 973209 (6.8x)</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>337.3</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="K117" s="7" t="n">
+        <v>372</v>
+      </c>
+      <c r="L117" s="8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M117" s="7" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="N117" s="8" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="O117" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="n">
+        <v>337.3</v>
+      </c>
+      <c r="R117" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.328.8 above EMA200 Rs.311.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 6.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 6.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 334.7</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>4932.2998046875</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2893800 / 752502 (3.8x)</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>4950</v>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>4999.5</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>4628</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>-0.07400000000000001</v>
+      </c>
+      <c r="K118" s="7" t="n">
+        <v>5742.5</v>
+      </c>
+      <c r="L118" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M118" s="7" t="n">
+        <v>6114</v>
+      </c>
+      <c r="N118" s="8" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="O118" s="4" t="n">
+        <v>4585</v>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>4999.5</v>
+      </c>
+      <c r="R118" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.4932.3 above EMA200 Rs.3842.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 4950.0</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>341</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>5739771 / 4641148 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K119" s="7" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="L119" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M119" s="7" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="N119" s="8" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O119" s="4" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="R119" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.341.0 above EMA200 Rs.285.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 341.5</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1692</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1055767 / 841355 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>1698.8</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>1710.6</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>1631.7</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K120" s="7" t="n">
+        <v>1868.4</v>
+      </c>
+      <c r="L120" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M120" s="7" t="n">
+        <v>1947.3</v>
+      </c>
+      <c r="N120" s="8" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O120" s="4" t="n">
+        <v>1653.099975585938</v>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>1710.6</v>
+      </c>
+      <c r="R120" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1692.0 above EMA200 Rs.1421.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1698.8</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 08:03 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T120"/>
+  <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9658,6 +9658,310 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>MRPL</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>184.4600067138672</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>47473688 / 9607844 (4.9x)</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K121" s="7" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="L121" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M121" s="7" t="n">
+        <v>222.8</v>
+      </c>
+      <c r="N121" s="8" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="O121" s="4" t="n">
+        <v>172.9600067138672</v>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="R121" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.184.5 above EMA200 Rs.163.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 4.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 4.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 187.0</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>JSWINFRA</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>341.3999938964844</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>5358907 / 2277436 (2.4x)</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K122" s="7" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="L122" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M122" s="7" t="n">
+        <v>396.9</v>
+      </c>
+      <c r="N122" s="8" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="O122" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="R122" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.341.4 above EMA200 Rs.302.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 343.5</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>1556</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>1253238 / 858333 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>1562</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>1572.6</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>1501.7</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="K123" s="7" t="n">
+        <v>1714.3</v>
+      </c>
+      <c r="L123" s="8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M123" s="7" t="n">
+        <v>1785.2</v>
+      </c>
+      <c r="N123" s="8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O123" s="4" t="n">
+        <v>1528.199951171875</v>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>1572.6</v>
+      </c>
+      <c r="R123" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1556.0 above EMA200 Rs.1554.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1562.0</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>1353.400024414062</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2870953 / 1950234 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>1376</v>
+      </c>
+      <c r="H124" s="4" t="n">
+        <v>1389.8</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>1282</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>-0.078</v>
+      </c>
+      <c r="K124" s="7" t="n">
+        <v>1605.3</v>
+      </c>
+      <c r="L124" s="8" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="M124" s="7" t="n">
+        <v>1713.1</v>
+      </c>
+      <c r="N124" s="8" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="O124" s="4" t="n">
+        <v>1302.300048828125</v>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>1389.8</v>
+      </c>
+      <c r="R124" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1353.4 above EMA200 Rs.1010.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1376.0</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 08:07 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T124"/>
+  <dimension ref="A1:T130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9962,6 +9962,462 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>116.8499984741211</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>18228404 / 11579461 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="K125" s="7" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="L125" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M125" s="7" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="N125" s="8" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O125" s="4" t="n">
+        <v>115.6100006103516</v>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="R125" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.116.8 above EMA200 Rs.111.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 118.2</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>500.2999877929688</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>4396774 / 2193697 (2.0x)</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="H126" s="4" t="n">
+        <v>518.2</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>493.1</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K126" s="7" t="n">
+        <v>568.4</v>
+      </c>
+      <c r="L126" s="8" t="n">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="M126" s="7" t="n">
+        <v>593.6</v>
+      </c>
+      <c r="N126" s="8" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O126" s="4" t="n">
+        <v>498.9500122070312</v>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>518.2</v>
+      </c>
+      <c r="R126" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.500.3 above EMA200 Rs.453.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.0x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.0x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 514.5</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>1658.300048828125</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>8084030 / 4724232 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>1661.9</v>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v>1678.5</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>1553.1</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="K127" s="7" t="n">
+        <v>1929.3</v>
+      </c>
+      <c r="L127" s="8" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M127" s="7" t="n">
+        <v>2054.7</v>
+      </c>
+      <c r="N127" s="8" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="O127" s="4" t="n">
+        <v>1580</v>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>1678.5</v>
+      </c>
+      <c r="R127" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1658.3 above EMA200 Rs.1026.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1661.9</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>JSWINFRA</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>342.4500122070312</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2841684 / 2124449 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K128" s="7" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M128" s="7" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="N128" s="8" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="O128" s="4" t="n">
+        <v>341.3999938964844</v>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="R128" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.342.5 above EMA200 Rs.302.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 345.0</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>1179</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>1084408 / 758435 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>1195.1</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>1137.1</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K129" s="7" t="n">
+        <v>1311.2</v>
+      </c>
+      <c r="L129" s="8" t="n">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="M129" s="7" t="n">
+        <v>1369.2</v>
+      </c>
+      <c r="N129" s="8" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O129" s="4" t="n">
+        <v>1142</v>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>1195.1</v>
+      </c>
+      <c r="R129" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1179.0 above EMA200 Rs.1016.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1186.4</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>288.7000122070312</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2585057 / 2103793 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="H130" s="4" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>281.6</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K130" s="7" t="n">
+        <v>314.8</v>
+      </c>
+      <c r="L130" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M130" s="7" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="N130" s="8" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="O130" s="4" t="n">
+        <v>285.8999938964844</v>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="R130" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.288.7 above EMA200 Rs.279.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 52 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 291.0</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T130"/>
+  <dimension ref="A1:T131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 07:58 PM IST</t>
+          <t>11/09/2026 07:57 PM IST</t>
         </is>
       </c>
     </row>
@@ -10415,6 +10415,82 @@
       <c r="T130" s="2" t="inlineStr">
         <is>
           <t>10/09/2026 07:58 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026 07:57 PM IST</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1424</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>3358624 / 1121622 (3.0x)</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H131" s="4" t="n">
+        <v>1513</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>1392</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K131" s="7" t="n">
+        <v>1755.1</v>
+      </c>
+      <c r="L131" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M131" s="7" t="n">
+        <v>1876.1</v>
+      </c>
+      <c r="N131" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O131" s="4" t="n">
+        <v>1418.400024414062</v>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>1513</v>
+      </c>
+      <c r="R131" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1424.0 above EMA200 Rs.1019.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 70 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.0x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.0x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1498.0</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026 07:57 PM IST</t>
         </is>
       </c>
     </row>
